--- a/kawasaki_project/05_試算・管理シート/川崎町_第10期_計画見込量_R8.9.15.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_第10期_計画見込量_R8.9.15.xlsx
@@ -25,7 +25,7 @@
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.000000"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="4">
@@ -97,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -117,6 +117,10 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -863,7 +867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1218,111 +1222,117 @@
         <v>639</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>推計</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>107</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>108</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>164</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>122</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>令和8年度を1.000とした伸び率</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>年度</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr"/>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>要支援1</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>要支援2</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>要介護1</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>要介護2</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>要介護3</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>要介護4</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>要介護5</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>令和9年度</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>1.054</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>0.985</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <v>1.038</v>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="I13" s="8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="J13" s="5" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>令和10年度</t>
+          <t>令和9年度</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="8" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>1.011</v>
+        <v>1.054</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>1.108</v>
+        <v>0.985</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0.9379999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>1.008</v>
+        <v>1.038</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>1.051</v>
+        <v>1.01</v>
       </c>
       <c r="I14" s="8" t="n">
         <v>1.02</v>
@@ -1332,7 +1342,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>令和11年度</t>
+          <t>令和10年度</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr"/>
@@ -1340,19 +1350,19 @@
         <v>1</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>1.043</v>
+        <v>1.011</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>1.123</v>
+        <v>1.108</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0.959</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="G15" s="8" t="n">
         <v>1.008</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>1.041</v>
+        <v>1.051</v>
       </c>
       <c r="I15" s="8" t="n">
         <v>1.02</v>
@@ -1362,62 +1372,122 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>令和12年度</t>
+          <t>令和11年度</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="8" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>1.033</v>
+        <v>1.043</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>1.154</v>
+        <v>1.123</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0.969</v>
+        <v>0.959</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>1</v>
+        <v>1.008</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>1.051</v>
+        <v>1.041</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>1.041</v>
+        <v>1.02</v>
       </c>
       <c r="J16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>令和17年度</t>
+          <t>令和12年度</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>1.033</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>1.051</v>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="J17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="8" t="n">
         <v>1.212</v>
       </c>
-      <c r="D17" s="8" t="n">
+      <c r="D18" s="8" t="n">
         <v>1.109</v>
       </c>
-      <c r="E17" s="8" t="n">
+      <c r="E18" s="8" t="n">
         <v>1.262</v>
       </c>
-      <c r="F17" s="8" t="n">
+      <c r="F18" s="8" t="n">
         <v>1.072</v>
       </c>
-      <c r="G17" s="8" t="n">
+      <c r="G18" s="8" t="n">
         <v>1.12</v>
       </c>
-      <c r="H17" s="8" t="n">
+      <c r="H18" s="8" t="n">
         <v>1.122</v>
       </c>
-      <c r="I17" s="8" t="n">
+      <c r="I18" s="8" t="n">
         <v>1.061</v>
       </c>
-      <c r="J17" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="8" t="n">
+        <v>1.242</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>1.113</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>1.233</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>1.245</v>
+      </c>
+      <c r="I19" s="8" t="n">
+        <v>1.245</v>
+      </c>
+      <c r="J19" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3967,7 +4037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4226,11 +4296,11 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>所得段階別加入割合による補正係数</t>
+          <t>所得段階別加入割合による補正係数（令和7年度末実績・13段階）</t>
         </is>
       </c>
       <c r="B15" s="14" t="n">
-        <v>0.964047</v>
+        <v>1.013748456790123</v>
       </c>
     </row>
     <row r="16">
@@ -4240,7 +4310,7 @@
         </is>
       </c>
       <c r="B16" s="11" t="n">
-        <v>9265.455717000001</v>
+        <v>9743.136418209875</v>
       </c>
     </row>
     <row r="17">
@@ -4260,173 +4330,541 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>7174.118765693686</v>
+        <v>6822.390334984808</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>【感度分析】所得段階別被保険者数（第10〜13段階が0人である影響）</t>
+          <t>【内訳】所得段階別第1号被保険者数（令和7年度末・年報 様式1 所得段階別 列20）</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ケース</t>
+          <t>段階</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>補正係数</t>
+          <t>基準額に対する乗率</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>保険料基準額（月額）</t>
+          <t>被保険者数（人）</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>基本との差</t>
+          <t>構成比</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>加重（人×乗率）</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>基本：現在の所得段階分布のまま</t>
-        </is>
-      </c>
-      <c r="B23" s="14" t="n">
-        <v>0.9640460000000001</v>
-      </c>
-      <c r="C23" s="17" t="n">
-        <v>7174.126207370499</v>
-      </c>
-      <c r="D23" s="17" t="n">
-        <v>0.007441676812959486</v>
+          <t>第1段階（軽減後 0.285）</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>383</v>
+      </c>
+      <c r="D23" s="15" t="n">
+        <v>0.1182098765432099</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>174.265</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>ケースB：第9段階を全国比で第9〜13段階に分解</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="n">
-        <v>0.9723242574568289</v>
-      </c>
-      <c r="C24" s="17" t="n">
-        <v>7113.046517835928</v>
-      </c>
-      <c r="D24" s="17" t="n">
-        <v>-61.07224785775816</v>
+          <t>第2段階（軽減後 0.485）</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>298</v>
+      </c>
+      <c r="D24" s="15" t="n">
+        <v>0.09197530864197531</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>204.13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>ケースC：全国並みに第10〜13段階が存在（第5段階から移動）</t>
-        </is>
-      </c>
-      <c r="B25" s="14" t="n">
-        <v>1.011516</v>
-      </c>
-      <c r="C25" s="17" t="n">
-        <v>6837.447626840011</v>
-      </c>
-      <c r="D25" s="17" t="n">
-        <v>-336.6711388536751</v>
+          <t>第3段階（軽減後 0.685）</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>305</v>
+      </c>
+      <c r="D25" s="15" t="n">
+        <v>0.0941358024691358</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>210.45</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>第4段階</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>343</v>
+      </c>
+      <c r="D26" s="15" t="n">
+        <v>0.1058641975308642</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>308.7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>第5段階</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>679</v>
+      </c>
+      <c r="D27" s="15" t="n">
+        <v>0.2095679012345679</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>679</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>【感度分析】準備基金の取崩し</t>
-        </is>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>第6段階</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>410</v>
+      </c>
+      <c r="D28" s="15" t="n">
+        <v>0.1265432098765432</v>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>492</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>第7段階</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>427</v>
+      </c>
+      <c r="D29" s="15" t="n">
+        <v>0.1317901234567901</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>555.1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>第8段階</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>232</v>
+      </c>
+      <c r="D30" s="15" t="n">
+        <v>0.07160493827160494</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>第9段階</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="D31" s="15" t="n">
+        <v>0.02623456790123457</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>144.5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>第10段階</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="D32" s="15" t="n">
+        <v>0.008024691358024692</v>
+      </c>
+      <c r="E32" s="11" t="n">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>第11段階</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="D33" s="15" t="n">
+        <v>0.005246913580246914</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>35.7</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>第12段階</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D34" s="15" t="n">
+        <v>0.002160493827160494</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>16.1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>第13段階</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="D35" s="15" t="n">
+        <v>0.008641975308641974</v>
+      </c>
+      <c r="E35" s="11" t="n">
+        <v>67.2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr"/>
+      <c r="C36" s="18" t="n">
+        <v>3240</v>
+      </c>
+      <c r="D36" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="20" t="n">
+        <v>3284.545</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>【比較】所得段階別の分布のとり方による保険料基準額</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>分布</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>補正係数</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>補正後被保険者数</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>保険料基準額（月額）</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>採用との差</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>見える化システムの現在の登録値（第10〜13段階が0人）</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="n">
+        <v>0.964047</v>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>9265.455717000001</v>
+      </c>
+      <c r="D40" s="21" t="n">
+        <v>7174.118765693686</v>
+      </c>
+      <c r="E40" s="21" t="n">
+        <v>351.7284307088785</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>令和6年度末の実績分布（13段階）</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="n">
+        <v>0.9974854339159769</v>
+      </c>
+      <c r="C41" s="11" t="n">
+        <v>9586.832505366454</v>
+      </c>
+      <c r="D41" s="21" t="n">
+        <v>6933.62272625756</v>
+      </c>
+      <c r="E41" s="21" t="n">
+        <v>111.2323912727525</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>令和7年度末の実績分布（13段階）★採用</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="n">
+        <v>1.013748456790123</v>
+      </c>
+      <c r="C42" s="11" t="n">
+        <v>9743.136418209875</v>
+      </c>
+      <c r="D42" s="21" t="n">
+        <v>6822.390334984808</v>
+      </c>
+      <c r="E42" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>※ 見える化システムには第10〜13段階が0人として登録されているため、補正係数が実績より 0.0497 低く出て、保険料が 352円／月 高く算定される。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>【感度分析】介護給付費準備基金の取崩し</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>取崩額（千円）</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>月額換算（円）</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>保険料基準額（月額）</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="n">
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>第9期6,500円との差</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="B30" s="5" t="n">
-        <v>-0</v>
-      </c>
-      <c r="C30" s="17" t="n">
-        <v>7174.118765693686</v>
-      </c>
-      <c r="D30" s="5" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="n">
-        <v>10000</v>
-      </c>
-      <c r="B31" s="5" t="n">
-        <v>-89.93981071048201</v>
-      </c>
-      <c r="C31" s="17" t="n">
-        <v>7084.178954983205</v>
-      </c>
-      <c r="D31" s="5" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="n">
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="21" t="n">
+        <v>6822.390334984808</v>
+      </c>
+      <c r="D48" s="21" t="n">
+        <v>322.3903349848079</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="B32" s="5" t="n">
-        <v>-269.819432131446</v>
-      </c>
-      <c r="C32" s="17" t="n">
-        <v>6904.29933356224</v>
-      </c>
-      <c r="D32" s="5" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="n">
+      <c r="B49" s="5" t="n">
+        <v>-256.5908853875344</v>
+      </c>
+      <c r="C49" s="21" t="n">
+        <v>6565.799449597273</v>
+      </c>
+      <c r="D49" s="21" t="n">
+        <v>65.79944959727345</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="n">
         <v>50000</v>
       </c>
-      <c r="B33" s="5" t="n">
-        <v>-449.6990535524101</v>
-      </c>
-      <c r="C33" s="17" t="n">
-        <v>6724.419712141276</v>
-      </c>
-      <c r="D33" s="5" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="n">
+      <c r="B50" s="5" t="n">
+        <v>-427.6514756458901</v>
+      </c>
+      <c r="C50" s="21" t="n">
+        <v>6394.738859338918</v>
+      </c>
+      <c r="D50" s="21" t="n">
+        <v>-105.2611406610822</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="n">
+        <v>76250</v>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>-652.1685003599823</v>
+      </c>
+      <c r="C51" s="21" t="n">
+        <v>6170.221834624826</v>
+      </c>
+      <c r="D51" s="21" t="n">
+        <v>-329.7781653751745</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="n">
         <v>78000</v>
       </c>
-      <c r="B34" s="5" t="n">
-        <v>-701.5305235417596</v>
-      </c>
-      <c r="C34" s="17" t="n">
-        <v>6472.588242151926</v>
-      </c>
-      <c r="D34" s="5" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="B52" s="5" t="n">
+        <v>-667.1363020075887</v>
+      </c>
+      <c r="C52" s="21" t="n">
+        <v>6155.254032977219</v>
+      </c>
+      <c r="D52" s="21" t="n">
+        <v>-344.7459670227809</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>-855.3029512917801</v>
+      </c>
+      <c r="C53" s="21" t="n">
+        <v>5967.087383693028</v>
+      </c>
+      <c r="D53" s="21" t="n">
+        <v>-532.9126163069723</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="n">
+        <v>152500</v>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>-1304.337000719965</v>
+      </c>
+      <c r="C54" s="21" t="n">
+        <v>5518.053334264843</v>
+      </c>
+      <c r="D54" s="21" t="n">
+        <v>-981.9466657351568</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>※ 基金残高は令和8年度末見込み152,500千円（町財政担当に確定値を照会中）。76,250千円は50％取崩し、152,500千円は全額取崩し。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>※ 第9期は78,000千円（月額698.59円相当）を取り崩し、条例上の基準額を6,508.33円としている。</t>
         </is>

--- a/kawasaki_project/05_試算・管理シート/川崎町_第10期_計画見込量_R8.9.15.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_第10期_計画見込量_R8.9.15.xlsx
@@ -1090,28 +1090,28 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>50</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>576</v>
+        <v>584</v>
       </c>
     </row>
     <row r="7">
@@ -1126,28 +1126,28 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -1162,28 +1162,28 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>585</v>
+        <v>590</v>
       </c>
     </row>
     <row r="9">
@@ -1198,28 +1198,28 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>52</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="10">
@@ -1234,28 +1234,28 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>61</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>688</v>
+        <v>694</v>
       </c>
     </row>
     <row r="12">
@@ -1347,22 +1347,22 @@
       </c>
       <c r="B15" s="5" t="inlineStr"/>
       <c r="C15" s="8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>1.065</v>
+      </c>
+      <c r="E15" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="8" t="n">
-        <v>1.011</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>1.108</v>
-      </c>
       <c r="F15" s="8" t="n">
-        <v>0.9379999999999999</v>
+        <v>1.031</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>1.008</v>
+        <v>1.038</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>1.051</v>
+        <v>1.01</v>
       </c>
       <c r="I15" s="8" t="n">
         <v>1.02</v>
@@ -1377,25 +1377,25 @@
       </c>
       <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>1.087</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>1.015</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>1.053</v>
+      </c>
+      <c r="H16" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="8" t="n">
-        <v>1.043</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>1.123</v>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>0.959</v>
-      </c>
-      <c r="G16" s="8" t="n">
-        <v>1.008</v>
-      </c>
-      <c r="H16" s="8" t="n">
+      <c r="I16" s="8" t="n">
         <v>1.041</v>
-      </c>
-      <c r="I16" s="8" t="n">
-        <v>1.02</v>
       </c>
       <c r="J16" s="5" t="inlineStr"/>
     </row>
@@ -1407,25 +1407,25 @@
       </c>
       <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="8" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>1.033</v>
+        <v>1.087</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>1.154</v>
+        <v>1.062</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.969</v>
+        <v>1.041</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>1</v>
+        <v>1.038</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>1.051</v>
+        <v>1.01</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>1.041</v>
+        <v>1.02</v>
       </c>
       <c r="J17" s="5" t="inlineStr"/>
     </row>
@@ -1437,22 +1437,22 @@
       </c>
       <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="8" t="n">
-        <v>1.212</v>
+        <v>1.121</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>1.109</v>
+        <v>1.152</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>1.262</v>
+        <v>1.123</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>1.072</v>
+        <v>1.196</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>1.12</v>
+        <v>1.143</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>1.122</v>
+        <v>1.071</v>
       </c>
       <c r="I18" s="8" t="n">
         <v>1.061</v>
@@ -1467,22 +1467,22 @@
       </c>
       <c r="B19" s="5" t="inlineStr"/>
       <c r="C19" s="8" t="n">
-        <v>1.242</v>
+        <v>1.212</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>1.163</v>
+        <v>1.217</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>1.308</v>
+        <v>1.185</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>1.113</v>
+        <v>1.237</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>1.233</v>
+        <v>1.271</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>1.245</v>
+        <v>1.173</v>
       </c>
       <c r="I19" s="8" t="n">
         <v>1.245</v>
@@ -1567,13 +1567,13 @@
         <v>173.6596363636364</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>168.552</v>
+        <v>173.6596363636364</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>168.552</v>
+        <v>173.6596363636364</v>
       </c>
       <c r="G2" s="10" t="n">
-        <v>510.7636363636364</v>
+        <v>520.9789090909092</v>
       </c>
     </row>
     <row r="3">
@@ -1594,10 +1594,10 @@
         <v>1.717171717171717</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1.666666666666667</v>
+        <v>1.717171717171717</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>1.666666666666667</v>
+        <v>1.717171717171717</v>
       </c>
       <c r="G3" s="5" t="n"/>
     </row>
@@ -1619,10 +1619,10 @@
         <v>0.4292929292929293</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4292929292929293</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4292929292929293</v>
       </c>
       <c r="G4" s="5" t="n"/>
     </row>
@@ -1644,13 +1644,13 @@
         <v>122.3072727272727</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>118.71</v>
+        <v>122.3072727272727</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>118.71</v>
+        <v>122.3072727272727</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>359.7272727272727</v>
+        <v>366.9218181818181</v>
       </c>
     </row>
     <row r="6">
@@ -1671,10 +1671,10 @@
         <v>2.919191919191919</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>2.833333333333333</v>
+        <v>2.919191919191919</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>2.833333333333333</v>
+        <v>2.919191919191919</v>
       </c>
       <c r="G6" s="5" t="n"/>
     </row>
@@ -1696,10 +1696,10 @@
         <v>1.03030303030303</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>1</v>
+        <v>1.03030303030303</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>1</v>
+        <v>1.03030303030303</v>
       </c>
       <c r="G7" s="5" t="n"/>
     </row>
@@ -1721,13 +1721,13 @@
         <v>2310.895568181818</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>2227.01175</v>
+        <v>2324.771318181819</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>2268.639</v>
+        <v>2352.522818181818</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>6806.546318181819</v>
+        <v>6988.189704545455</v>
       </c>
     </row>
     <row r="9">
@@ -1748,10 +1748,10 @@
         <v>60.201608476065</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>58.02264492753623</v>
+        <v>60.55758673693456</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>59.09057971014493</v>
+        <v>61.26954325867369</v>
       </c>
       <c r="G9" s="5" t="n"/>
     </row>
@@ -1773,10 +1773,10 @@
         <v>5.481225296442688</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>5.282608695652174</v>
+        <v>5.513833992094862</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>5.380434782608695</v>
+        <v>5.57905138339921</v>
       </c>
       <c r="G10" s="5" t="n"/>
     </row>
@@ -1798,13 +1798,13 @@
         <v>17947.72132509882</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>17233.02211956522</v>
+        <v>18110.59444466403</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>17721.64147826087</v>
+        <v>18436.34068379446</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>52902.3849229249</v>
+        <v>54494.65645355731</v>
       </c>
     </row>
     <row r="12">
@@ -1850,10 +1850,10 @@
         <v>36.38241106719368</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>34.96739130434783</v>
+        <v>36.68313570487484</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>35.8695652173913</v>
+        <v>37.28458498023716</v>
       </c>
       <c r="G13" s="5" t="n"/>
     </row>
@@ -1875,13 +1875,13 @@
         <v>39.64558695652174</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>38.01071739130435</v>
+        <v>40.05430434782609</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>39.23686956521739</v>
+        <v>40.87173913043478</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>116.8931739130435</v>
+        <v>120.5716304347826</v>
       </c>
     </row>
     <row r="15">
@@ -1902,10 +1902,10 @@
         <v>0.4393115942028986</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>0.4211956521739131</v>
+        <v>0.443840579710145</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.4528985507246377</v>
       </c>
       <c r="G15" s="5" t="n"/>
     </row>
@@ -1927,10 +1927,10 @@
         <v>0.08786231884057971</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>0.08423913043478261</v>
+        <v>0.08876811594202899</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>0.08695652173913043</v>
+        <v>0.09057971014492754</v>
       </c>
       <c r="G16" s="5" t="n"/>
     </row>
@@ -1952,13 +1952,13 @@
         <v>47.27484782608696</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>45.32536956521739</v>
+        <v>47.76221739130435</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>46.78747826086956</v>
+        <v>48.73695652173913</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>139.3876956521739</v>
+        <v>143.7740217391304</v>
       </c>
     </row>
     <row r="18">
@@ -1979,10 +1979,10 @@
         <v>0.3514492753623188</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.3369565217391304</v>
+        <v>0.355072463768116</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.3623188405797101</v>
       </c>
       <c r="G18" s="5" t="n"/>
     </row>
@@ -2004,10 +2004,10 @@
         <v>0.08786231884057971</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.08423913043478261</v>
+        <v>0.08876811594202899</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.08695652173913043</v>
+        <v>0.09057971014492754</v>
       </c>
       <c r="G19" s="5" t="n"/>
     </row>
@@ -2029,13 +2029,13 @@
         <v>3410.895325098814</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>3275.969119565218</v>
+        <v>3441.064444664032</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>3366.476478260869</v>
+        <v>3501.402683794466</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>10053.3409229249</v>
+        <v>10353.36245355731</v>
       </c>
     </row>
     <row r="21">
@@ -2056,10 +2056,10 @@
         <v>38.48309178743961</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>36.98550724637681</v>
+        <v>38.80193236714976</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>37.94202898550724</v>
+        <v>39.43961352657004</v>
       </c>
       <c r="G21" s="5" t="n"/>
     </row>
@@ -2081,13 +2081,13 @@
         <v>84.14960869565218</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>80.67952173913044</v>
+        <v>85.01713043478262</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>83.28208695652174</v>
+        <v>86.75217391304348</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>248.1112173913043</v>
+        <v>255.9189130434783</v>
       </c>
     </row>
     <row r="23">
@@ -2108,10 +2108,10 @@
         <v>0.2635869565217391</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.2527173913043478</v>
+        <v>0.266304347826087</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.2608695652173913</v>
+        <v>0.2717391304347826</v>
       </c>
       <c r="G23" s="5" t="n"/>
     </row>
@@ -2133,13 +2133,13 @@
         <v>369.1271739130435</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>353.9054347826087</v>
+        <v>372.9326086956522</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>365.3217391304348</v>
+        <v>380.5434782608696</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>1088.354347826087</v>
+        <v>1122.603260869565</v>
       </c>
     </row>
     <row r="25">
@@ -2160,10 +2160,10 @@
         <v>0.3514492753623188</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.3369565217391304</v>
+        <v>0.355072463768116</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.3623188405797101</v>
       </c>
       <c r="G25" s="5" t="n"/>
     </row>
@@ -2185,13 +2185,13 @@
         <v>4585.679217391305</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>4396.579043478261</v>
+        <v>4632.954260869566</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>4538.404173913043</v>
+        <v>4727.504347826087</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>13520.66243478261</v>
+        <v>13946.13782608696</v>
       </c>
     </row>
     <row r="27">
@@ -2212,10 +2212,10 @@
         <v>1.493659420289855</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>1.432065217391304</v>
+        <v>1.509057971014493</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>1.478260869565218</v>
+        <v>1.539855072463768</v>
       </c>
       <c r="G27" s="5" t="n"/>
     </row>
@@ -2237,13 +2237,13 @@
         <v>4833.249472990778</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>4647.775652173913</v>
+        <v>4871.01512516469</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>4761.072608695652</v>
+        <v>4946.546429512517</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>14242.09773386034</v>
+        <v>14650.81102766798</v>
       </c>
     </row>
     <row r="29">
@@ -2264,10 +2264,10 @@
         <v>62.63059947299077</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>60.23369565217391</v>
+        <v>63.11429512516469</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>61.68478260869565</v>
+        <v>64.08168642951252</v>
       </c>
       <c r="G29" s="5" t="n"/>
     </row>
@@ -2289,13 +2289,13 @@
         <v>33924.60503524375</v>
       </c>
       <c r="E31" s="13" t="n">
-        <v>32585.54072826088</v>
+        <v>34222.13276350461</v>
       </c>
       <c r="F31" s="13" t="n">
-        <v>33478.12391304348</v>
+        <v>34817.18822002635</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>99988.26967654811</v>
+        <v>102963.9260187747</v>
       </c>
     </row>
   </sheetData>
@@ -2376,13 +2376,13 @@
         <v>28301.99500786982</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>28287.99525127731</v>
+        <v>28449.28213982859</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>28403.16788323607</v>
+        <v>28760.58766066639</v>
       </c>
       <c r="G2" s="10" t="n">
-        <v>84993.15814238321</v>
+        <v>85511.8648083648</v>
       </c>
     </row>
     <row r="3">
@@ -2403,10 +2403,10 @@
         <v>719.1715742213242</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>717.5460091048399</v>
+        <v>722.6501890772587</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>720.287379062815</v>
+        <v>730.9183574377203</v>
       </c>
       <c r="G3" s="5" t="n"/>
     </row>
@@ -2428,10 +2428,10 @@
         <v>33.69582504607502</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>33.66450894853538</v>
+        <v>33.95695377988417</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>33.88397101567787</v>
+        <v>34.25165826086685</v>
       </c>
       <c r="G4" s="5" t="n"/>
     </row>
@@ -2453,13 +2453,13 @@
         <v>2722.576250340505</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>2652.682606979525</v>
+        <v>2741.018580237412</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>2666.44829401929</v>
+        <v>2758.890334802396</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>8041.70715133932</v>
+        <v>8222.485165380313</v>
       </c>
     </row>
     <row r="6">
@@ -2480,10 +2480,10 @@
         <v>17.52421785317491</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>17.07314078642852</v>
+        <v>17.639338128089</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>17.16019983685281</v>
+        <v>17.76290597628091</v>
       </c>
       <c r="G6" s="5" t="n"/>
     </row>
@@ -2505,10 +2505,10 @@
         <v>3.907640972829718</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>3.802542992237589</v>
+        <v>3.936850594822845</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>3.824949893142282</v>
+        <v>3.960391590168352</v>
       </c>
       <c r="G7" s="5" t="n"/>
     </row>
@@ -2530,13 +2530,13 @@
         <v>3075.395432501442</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>2924.144405867166</v>
+        <v>3120.304967156477</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>2965.585267052814</v>
+        <v>3125.420827323378</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>8965.125105421423</v>
+        <v>9321.121226981297</v>
       </c>
     </row>
     <row r="9">
@@ -2557,10 +2557,10 @@
         <v>57.87668682440211</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>54.47228768505607</v>
+        <v>58.86850548683933</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>55.42584104137084</v>
+        <v>58.9179567248244</v>
       </c>
       <c r="G9" s="5" t="n"/>
     </row>
@@ -2582,10 +2582,10 @@
         <v>7.101151407180009</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>6.79228803713146</v>
+        <v>7.19693517667512</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>6.877017384857864</v>
+        <v>7.206854893549724</v>
       </c>
       <c r="G10" s="5" t="n"/>
     </row>
@@ -2607,13 +2607,13 @@
         <v>4801.536378643703</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>4565.61676342655</v>
+        <v>4867.275636534267</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>4630.341133562011</v>
+        <v>4890.36810146858</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>13997.49427563226</v>
+        <v>14559.18011664655</v>
       </c>
     </row>
     <row r="12">
@@ -2634,10 +2634,10 @@
         <v>116.0107021831229</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>110.2020390701462</v>
+        <v>117.6195311548385</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>111.7870585180522</v>
+        <v>118.1603089234358</v>
       </c>
       <c r="G12" s="5" t="n"/>
     </row>
@@ -2659,10 +2659,10 @@
         <v>9.214790892775158</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>8.81735987896557</v>
+        <v>9.350040694519803</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>8.951759340574162</v>
+        <v>9.395906044708463</v>
       </c>
       <c r="G13" s="5" t="n"/>
     </row>
@@ -2684,13 +2684,13 @@
         <v>1235.210000242847</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>1229.88997315252</v>
+        <v>1244.463831646495</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>1236.036875984739</v>
+        <v>1250.795350831821</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>3701.136849380106</v>
+        <v>3730.469182721162</v>
       </c>
     </row>
     <row r="15">
@@ -2711,10 +2711,10 @@
         <v>8.295627039162424</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>8.181803878110367</v>
+        <v>8.364302693405088</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>8.235173409904052</v>
+        <v>8.414480335312053</v>
       </c>
       <c r="G15" s="5" t="n"/>
     </row>
@@ -2736,13 +2736,13 @@
         <v>63412.88672517361</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>63316.2653729193</v>
+        <v>63818.09502033618</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>63600.40724971452</v>
+        <v>64296.93661862587</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>190329.5593478074</v>
+        <v>191527.9183641357</v>
       </c>
     </row>
     <row r="17">
@@ -2763,10 +2763,10 @@
         <v>543.4846353592148</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>543.6503841596741</v>
+        <v>547.4089282484562</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>546.6478063006161</v>
+        <v>551.5970028305157</v>
       </c>
       <c r="G17" s="5" t="n"/>
     </row>
@@ -2788,10 +2788,10 @@
         <v>53.89416896438445</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>54.14672985851964</v>
+        <v>54.3644438784738</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>54.54727688145253</v>
+        <v>54.80914491678385</v>
       </c>
       <c r="G18" s="5" t="n"/>
     </row>
@@ -2813,13 +2813,13 @@
         <v>100180.2429881359</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>98540.99799780587</v>
+        <v>101056.1713194603</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>99319.99205361999</v>
+        <v>101816.0329625157</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>298041.2330395618</v>
+        <v>303052.4472701119</v>
       </c>
     </row>
     <row r="20">
@@ -2840,10 +2840,10 @@
         <v>773.0922688575409</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>761.4816597898392</v>
+        <v>780.482025664308</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>768.2447159163344</v>
+        <v>786.3875098417847</v>
       </c>
       <c r="G20" s="5" t="n"/>
     </row>
@@ -2865,10 +2865,10 @@
         <v>88.20983518329074</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>87.02259125779783</v>
+        <v>89.16863772095924</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>87.91846862539832</v>
+        <v>89.81006822028449</v>
       </c>
       <c r="G21" s="5" t="n"/>
     </row>
@@ -2890,13 +2890,13 @@
         <v>16098.44922811623</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>16220.03760550737</v>
+        <v>16128.61614294573</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>16171.88266319401</v>
+        <v>16163.41010855756</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>48490.36949681761</v>
+        <v>48390.47547961952</v>
       </c>
     </row>
     <row r="23">
@@ -2917,10 +2917,10 @@
         <v>141.1668926834476</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>142.0266032206948</v>
+        <v>141.4870354273017</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>141.6860316788346</v>
+        <v>141.8142249670852</v>
       </c>
       <c r="G23" s="5" t="n"/>
     </row>
@@ -2942,10 +2942,10 @@
         <v>15.44589098212848</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>15.4568458503231</v>
+        <v>15.51494993005341</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>15.4816871111732</v>
+        <v>15.61026376408905</v>
       </c>
       <c r="G24" s="5" t="n"/>
     </row>
@@ -2967,13 +2967,13 @@
         <v>8809.597999697271</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>8766.166168651036</v>
+        <v>8842.062602710754</v>
       </c>
       <c r="F25" s="10" t="n">
-        <v>8779.686506358395</v>
+        <v>8912.626714765616</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>26355.45067470671</v>
+        <v>26564.28731717364</v>
       </c>
     </row>
     <row r="26">
@@ -2994,10 +2994,10 @@
         <v>60.22551038863728</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>59.93104078310652</v>
+        <v>60.47379217557886</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>60.05347222991205</v>
+        <v>60.94971412330532</v>
       </c>
       <c r="G26" s="5" t="n"/>
     </row>
@@ -3019,10 +3019,10 @@
         <v>8.60067842655239</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>8.600476522676354</v>
+        <v>8.634527223803248</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>8.620719877750341</v>
+        <v>8.720205705722332</v>
       </c>
       <c r="G27" s="5" t="n"/>
     </row>
@@ -3044,13 +3044,13 @@
         <v>20862.79666684864</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>20417.19123274276</v>
+        <v>21045.82350602389</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>20569.00628620373</v>
+        <v>21171.04672696911</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>61848.99418579512</v>
+        <v>63079.66689984164</v>
       </c>
     </row>
     <row r="29">
@@ -3071,10 +3071,10 @@
         <v>130.3973094626222</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>127.8718553066704</v>
+        <v>131.6231355265926</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>128.9106065407089</v>
+        <v>132.3836811213487</v>
       </c>
       <c r="G29" s="5" t="n"/>
     </row>
@@ -3096,13 +3096,13 @@
         <v>581.1729199632705</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>568.8364407425611</v>
+        <v>589.2952311448724</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>576.3627315159997</v>
+        <v>591.7383624511602</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>1726.372092221831</v>
+        <v>1762.206513559303</v>
       </c>
     </row>
     <row r="31">
@@ -3123,10 +3123,10 @@
         <v>1.601719675306994</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>1.577649118831973</v>
+        <v>1.621029746678921</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>1.595258509931791</v>
+        <v>1.630335979293424</v>
       </c>
       <c r="G31" s="5" t="n"/>
     </row>
@@ -3148,13 +3148,13 @@
         <v>1013.847691551298</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>1014.815100795492</v>
+        <v>1029.258118196817</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>1028.829609073664</v>
+        <v>1033.072393004716</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>3057.492401420453</v>
+        <v>3076.178202752832</v>
       </c>
     </row>
     <row r="33">
@@ -3175,10 +3175,10 @@
         <v>0.8377571179563272</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.8487678213319637</v>
+        <v>0.848476124036158</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>0.8577861471396856</v>
+        <v>0.8518747304422832</v>
       </c>
       <c r="G33" s="5" t="n"/>
     </row>
@@ -3200,13 +3200,13 @@
         <v>6387.479180021994</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>6178.229991288349</v>
+        <v>6446.161513725404</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>6231.994284175433</v>
+        <v>6489.2930803122</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>18797.70345548577</v>
+        <v>19322.9337740596</v>
       </c>
     </row>
     <row r="35">
@@ -3227,10 +3227,10 @@
         <v>2.721690384906415</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>2.629725767346882</v>
+        <v>2.748309470288387</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>2.654644172456746</v>
+        <v>2.766716752229503</v>
       </c>
       <c r="G35" s="5" t="n"/>
     </row>
@@ -3252,13 +3252,13 @@
         <v>382.7712</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>430.6176</v>
+        <v>388.752</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>436.5984</v>
+        <v>394.7328</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>1249.9872</v>
+        <v>1166.256</v>
       </c>
     </row>
     <row r="37">
@@ -3279,10 +3279,10 @@
         <v>0.4102564102564103</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.4615384615384615</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>0.4679487179487179</v>
+        <v>0.4230769230769231</v>
       </c>
       <c r="G37" s="5" t="n"/>
     </row>
@@ -3304,13 +3304,13 @@
         <v>374.1240333068993</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>401.1872616970658</v>
+        <v>380.4494845360825</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>407.512712926249</v>
+        <v>384.727946074544</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>1182.824007930214</v>
+        <v>1139.301463917526</v>
       </c>
     </row>
     <row r="39">
@@ -3331,10 +3331,10 @@
         <v>8.090272270684641</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>8.721186888712662</v>
+        <v>8.225945017182131</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>8.856859635210151</v>
+        <v>8.322098863335976</v>
       </c>
       <c r="G39" s="5" t="n"/>
     </row>
@@ -3356,10 +3356,10 @@
         <v>0.9068464181866244</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.987126619085382</v>
+        <v>0.9218213058419243</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>1.002101506740682</v>
+        <v>0.9333597673803858</v>
       </c>
       <c r="G40" s="5" t="n"/>
     </row>
@@ -3381,13 +3381,13 @@
         <v>81115.10621855124</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>80774.59605433737</v>
+        <v>82018.19022949494</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>81658.50235099536</v>
+        <v>82764.20790555874</v>
       </c>
       <c r="G41" s="10" t="n">
-        <v>243548.204623884</v>
+        <v>245897.5043536049</v>
       </c>
     </row>
     <row r="42">
@@ -3408,10 +3408,10 @@
         <v>24.80621943297124</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>24.76550295104477</v>
+        <v>25.08663180410525</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>25.03996294122641</v>
+        <v>25.31592825952953</v>
       </c>
       <c r="G42" s="5" t="n"/>
     </row>
@@ -3433,13 +3433,13 @@
         <v>98308.21910305401</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>98656.235505736</v>
+        <v>98374.66267006432</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>98335.90985846058</v>
+        <v>98939.50358359817</v>
       </c>
       <c r="G43" s="10" t="n">
-        <v>295300.3644672506</v>
+        <v>295622.3853567165</v>
       </c>
     </row>
     <row r="44">
@@ -3460,10 +3460,10 @@
         <v>27.17044175239277</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>27.24364021246046</v>
+        <v>27.1910603090938</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>27.15711591201863</v>
+        <v>27.3411677204794</v>
       </c>
       <c r="G44" s="5" t="n"/>
     </row>
@@ -3488,10 +3488,10 @@
         <v>825.2204081632653</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>825.2204081632653</v>
+        <v>841.7248163265307</v>
       </c>
       <c r="G45" s="10" t="n">
-        <v>2475.661224489796</v>
+        <v>2492.165632653061</v>
       </c>
     </row>
     <row r="46">
@@ -3515,7 +3515,7 @@
         <v>0.2551020408163265</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>0.2551020408163265</v>
+        <v>0.2602040816326531</v>
       </c>
       <c r="G46" s="5" t="n"/>
     </row>
@@ -3537,13 +3537,13 @@
         <v>238204.5256679758</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>238252.5904043735</v>
+        <v>238425.0152900218</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>237772.3368631542</v>
+        <v>240460.9591619709</v>
       </c>
       <c r="G47" s="10" t="n">
-        <v>714229.4529355034</v>
+        <v>717090.5001199686</v>
       </c>
     </row>
     <row r="48">
@@ -3564,10 +3564,10 @@
         <v>69.36308565539827</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>69.33927435701523</v>
+        <v>69.4394800513803</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>69.21243746048025</v>
+        <v>70.01902988750908</v>
       </c>
       <c r="G48" s="5" t="n"/>
     </row>
@@ -3589,13 +3589,13 @@
         <v>265252.6766211779</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>264961.2417175412</v>
+        <v>266263.7245007973</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>265005.5548930789</v>
+        <v>267369.2095007229</v>
       </c>
       <c r="G49" s="10" t="n">
-        <v>795219.473231798</v>
+        <v>798885.6106226981</v>
       </c>
     </row>
     <row r="50">
@@ -3616,10 +3616,10 @@
         <v>67.80721161831734</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>67.66166501702314</v>
+        <v>68.10422457100039</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>67.72313375201911</v>
+        <v>68.38968203333756</v>
       </c>
       <c r="G50" s="5" t="n"/>
     </row>
@@ -3641,13 +3641,13 @@
         <v>42525.15043878565</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>42196.64593531058</v>
+        <v>42918.07979056994</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>42534.43618505407</v>
+        <v>43217.22734677915</v>
       </c>
       <c r="G51" s="10" t="n">
-        <v>127256.2325591503</v>
+        <v>128660.4575761347</v>
       </c>
     </row>
     <row r="52">
@@ -3668,10 +3668,10 @@
         <v>199.4036176100725</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>197.8122177469844</v>
+        <v>201.4518729629671</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>199.6385343243687</v>
+        <v>202.8379624999964</v>
       </c>
       <c r="G52" s="5" t="n"/>
     </row>
@@ -3693,13 +3693,13 @@
         <v>984470.9801601215</v>
       </c>
       <c r="E54" s="13" t="n">
-        <v>981181.2037983149</v>
+        <v>988971.9229835948</v>
       </c>
       <c r="F54" s="13" t="n">
-        <v>983155.8125095433</v>
+        <v>995632.5123033256</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>2948807.99646798</v>
+        <v>2969075.415447042</v>
       </c>
     </row>
   </sheetData>
@@ -3769,13 +3769,13 @@
         <v>29338.92581785244</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>28188.96168478261</v>
+        <v>29589.17850263504</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>28939.71973913044</v>
+        <v>30089.68387220026</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>86467.60724176548</v>
+        <v>89017.78819268773</v>
       </c>
     </row>
     <row r="3">
@@ -3791,13 +3791,13 @@
         <v>295202.9733693404</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>292358.3101250384</v>
+        <v>297444.1687794911</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>294151.5142596788</v>
+        <v>299609.3390711626</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>881712.7977540576</v>
+        <v>892256.4812199941</v>
       </c>
     </row>
     <row r="4">
@@ -3813,13 +3813,13 @@
         <v>4585.679217391305</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>4396.579043478261</v>
+        <v>4632.954260869566</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>4538.404173913043</v>
+        <v>4727.504347826087</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>13520.66243478261</v>
+        <v>13946.13782608696</v>
       </c>
     </row>
     <row r="5">
@@ -3835,13 +3835,13 @@
         <v>87502.58539857324</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>86952.82604562571</v>
+        <v>88464.35174322034</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>87890.4966351708</v>
+        <v>89253.50098587094</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>262345.9080793698</v>
+        <v>265220.4381276645</v>
       </c>
     </row>
     <row r="6">
@@ -3857,13 +3857,13 @@
         <v>601765.4213922077</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>601870.0676276507</v>
+        <v>603063.4024608834</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>601113.8016146936</v>
+        <v>606769.672246292</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>1804749.290634552</v>
+        <v>1811598.496099383</v>
       </c>
     </row>
     <row r="7">
@@ -3879,13 +3879,13 @@
         <v>1018395.585195365</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>1013766.744526576</v>
+        <v>1023194.055747099</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>1016633.936422587</v>
+        <v>1030449.700523352</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>3048796.266144527</v>
+        <v>3072039.341465816</v>
       </c>
     </row>
   </sheetData>
@@ -4084,13 +4084,13 @@
         <v>1018395585.195365</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>1013766744.526576</v>
+        <v>1023194055.747099</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>1016633936.422587</v>
+        <v>1030449700.523352</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>3048796266.144527</v>
+        <v>3072039341.465816</v>
       </c>
     </row>
     <row r="3">
@@ -4103,13 +4103,13 @@
         <v>54126758.52089445</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>54185356.08175548</v>
+        <v>54208016.43968906</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>54083274.46993785</v>
+        <v>54565709.81329891</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>162395389.0725878</v>
+        <v>162900484.7738824</v>
       </c>
     </row>
     <row r="4">
@@ -4122,13 +4122,13 @@
         <v>31083743.7389868</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>30942461.02012108</v>
+        <v>31230203.94672677</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>31029974.2217116</v>
+        <v>31451662.6864982</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>93056178.98081948</v>
+        <v>93765610.37221177</v>
       </c>
     </row>
     <row r="5">
@@ -4141,13 +4141,13 @@
         <v>2563573.233258635</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>2551921.207059748</v>
+        <v>2575652.26310306</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>2559138.693570964</v>
+        <v>2593916.655652313</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>7674633.133889345</v>
+        <v>7733142.152014008</v>
       </c>
     </row>
     <row r="6">
@@ -4160,13 +4160,13 @@
         <v>669000</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>665940</v>
+        <v>672120</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>667860</v>
+        <v>676920</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>2002800</v>
+        <v>2018040</v>
       </c>
     </row>
     <row r="7">
@@ -4179,13 +4179,13 @@
         <v>1106838660.688505</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>1102112422.835512</v>
+        <v>1111880048.396618</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>1104974183.807807</v>
+        <v>1119737909.678801</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>3313925267.331824</v>
+        <v>3338456618.763925</v>
       </c>
     </row>
     <row r="8">
@@ -4217,13 +4217,13 @@
         <v>265160503.5783561</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>264892986.2421678</v>
+        <v>267139540.1212222</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>266370708.6357956</v>
+        <v>269766365.5861243</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>796424198.4563196</v>
+        <v>802066409.2857027</v>
       </c>
     </row>
     <row r="10">
@@ -4236,13 +4236,13 @@
         <v>55681242.23442525</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>55430915.49177561</v>
+        <v>55919296.76983092</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>55559988.64039035</v>
+        <v>56298174.93394007</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>166672146.3665912</v>
+        <v>167898713.9381962</v>
       </c>
     </row>
     <row r="11">
@@ -4255,13 +4255,13 @@
         <v>68376565.46387421</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>65741065.77324587</v>
+        <v>66320285.96901947</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>63227267.07276422</v>
+        <v>64067323.07482379</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>197344898.3098843</v>
+        <v>198764174.5077175</v>
       </c>
     </row>
     <row r="12">
@@ -4274,13 +4274,13 @@
         <v>252465180.3489072</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>254582835.9606975</v>
+        <v>256738550.9220337</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>258703430.2034218</v>
+        <v>261997217.4452406</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>765751446.5130265</v>
+        <v>771200948.7161814</v>
       </c>
     </row>
     <row r="14">
@@ -4330,7 +4330,7 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>6822.390334984808</v>
+        <v>6870.942161208031</v>
       </c>
     </row>
     <row r="21">
@@ -4678,10 +4678,10 @@
         <v>9265.455717000001</v>
       </c>
       <c r="D40" s="21" t="n">
-        <v>7174.118765693686</v>
+        <v>7225.173682008072</v>
       </c>
       <c r="E40" s="21" t="n">
-        <v>351.7284307088785</v>
+        <v>354.2315208000409</v>
       </c>
     </row>
     <row r="41">
@@ -4697,10 +4697,10 @@
         <v>9586.832505366454</v>
       </c>
       <c r="D41" s="21" t="n">
-        <v>6933.62272625756</v>
+        <v>6982.966142446514</v>
       </c>
       <c r="E41" s="21" t="n">
-        <v>111.2323912727525</v>
+        <v>112.0239812384825</v>
       </c>
     </row>
     <row r="42">
@@ -4716,7 +4716,7 @@
         <v>9743.136418209875</v>
       </c>
       <c r="D42" s="21" t="n">
-        <v>6822.390334984808</v>
+        <v>6870.942161208031</v>
       </c>
       <c r="E42" s="21" t="n">
         <v>0</v>
@@ -4766,10 +4766,10 @@
         <v>0</v>
       </c>
       <c r="C48" s="21" t="n">
-        <v>6822.390334984808</v>
+        <v>6870.942161208031</v>
       </c>
       <c r="D48" s="21" t="n">
-        <v>322.3903349848079</v>
+        <v>370.9421612080314</v>
       </c>
     </row>
     <row r="49">
@@ -4780,10 +4780,10 @@
         <v>-256.5908853875344</v>
       </c>
       <c r="C49" s="21" t="n">
-        <v>6565.799449597273</v>
+        <v>6614.351275820497</v>
       </c>
       <c r="D49" s="21" t="n">
-        <v>65.79944959727345</v>
+        <v>114.351275820497</v>
       </c>
     </row>
     <row r="50">
@@ -4794,10 +4794,10 @@
         <v>-427.6514756458901</v>
       </c>
       <c r="C50" s="21" t="n">
-        <v>6394.738859338918</v>
+        <v>6443.290685562141</v>
       </c>
       <c r="D50" s="21" t="n">
-        <v>-105.2611406610822</v>
+        <v>-56.70931443785867</v>
       </c>
     </row>
     <row r="51">
@@ -4808,10 +4808,10 @@
         <v>-652.1685003599823</v>
       </c>
       <c r="C51" s="21" t="n">
-        <v>6170.221834624826</v>
+        <v>6218.773660848049</v>
       </c>
       <c r="D51" s="21" t="n">
-        <v>-329.7781653751745</v>
+        <v>-281.2263391519509</v>
       </c>
     </row>
     <row r="52">
@@ -4822,10 +4822,10 @@
         <v>-667.1363020075887</v>
       </c>
       <c r="C52" s="21" t="n">
-        <v>6155.254032977219</v>
+        <v>6203.805859200443</v>
       </c>
       <c r="D52" s="21" t="n">
-        <v>-344.7459670227809</v>
+        <v>-296.1941407995573</v>
       </c>
     </row>
     <row r="53">
@@ -4836,10 +4836,10 @@
         <v>-855.3029512917801</v>
       </c>
       <c r="C53" s="21" t="n">
-        <v>5967.087383693028</v>
+        <v>6015.639209916251</v>
       </c>
       <c r="D53" s="21" t="n">
-        <v>-532.9126163069723</v>
+        <v>-484.3607900837487</v>
       </c>
     </row>
     <row r="54">
@@ -4850,10 +4850,10 @@
         <v>-1304.337000719965</v>
       </c>
       <c r="C54" s="21" t="n">
-        <v>5518.053334264843</v>
+        <v>5566.605160488067</v>
       </c>
       <c r="D54" s="21" t="n">
-        <v>-981.9466657351568</v>
+        <v>-933.3948395119332</v>
       </c>
     </row>
     <row r="57">
